--- a/dev/StructureDefinition-educational-attainment.xlsx
+++ b/dev/StructureDefinition-educational-attainment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T05:11:07+00:00</t>
+    <t>2026-03-16T07:24:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-educational-attainment.xlsx
+++ b/dev/StructureDefinition-educational-attainment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T07:24:26+00:00</t>
+    <t>2026-03-16T20:48:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-educational-attainment.xlsx
+++ b/dev/StructureDefinition-educational-attainment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T20:48:05+00:00</t>
+    <t>2026-03-16T20:59:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-educational-attainment.xlsx
+++ b/dev/StructureDefinition-educational-attainment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T20:59:47+00:00</t>
+    <t>2026-03-16T21:16:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-educational-attainment.xlsx
+++ b/dev/StructureDefinition-educational-attainment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T21:16:15+00:00</t>
+    <t>2026-03-16T21:44:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-educational-attainment.xlsx
+++ b/dev/StructureDefinition-educational-attainment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T21:44:19+00:00</t>
+    <t>2026-03-16T21:58:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-educational-attainment.xlsx
+++ b/dev/StructureDefinition-educational-attainment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T21:58:37+00:00</t>
+    <t>2026-03-16T22:06:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-educational-attainment.xlsx
+++ b/dev/StructureDefinition-educational-attainment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T22:06:54+00:00</t>
+    <t>2026-03-16T22:26:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-educational-attainment.xlsx
+++ b/dev/StructureDefinition-educational-attainment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T22:26:22+00:00</t>
+    <t>2026-03-19T20:53:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-educational-attainment.xlsx
+++ b/dev/StructureDefinition-educational-attainment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T20:53:49+00:00</t>
+    <t>2026-03-19T21:27:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-educational-attainment.xlsx
+++ b/dev/StructureDefinition-educational-attainment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T21:27:42+00:00</t>
+    <t>2026-04-08T04:20:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-educational-attainment.xlsx
+++ b/dev/StructureDefinition-educational-attainment.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T04:20:57+00:00</t>
+    <t>2026-04-10T05:32:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-educational-attainment.xlsx
+++ b/dev/StructureDefinition-educational-attainment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T05:32:03+00:00</t>
+    <t>2026-04-10T05:44:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-educational-attainment.xlsx
+++ b/dev/StructureDefinition-educational-attainment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T05:44:36+00:00</t>
+    <t>2026-05-26T03:51:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -344,7 +344,7 @@
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
-    <t>required</t>
+    <t>extensible</t>
   </si>
   <si>
     <t>http://doh.gov.ph/fhir/ph-core/ValueSet/educational-attainments</t>

--- a/dev/StructureDefinition-educational-attainment.xlsx
+++ b/dev/StructureDefinition-educational-attainment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T03:51:01+00:00</t>
+    <t>2026-05-26T04:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-educational-attainment.xlsx
+++ b/dev/StructureDefinition-educational-attainment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T04:00:40+00:00</t>
+    <t>2026-05-26T04:36:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
